--- a/Impact modelling/Runs_food_municipalities_months.xlsx
+++ b/Impact modelling/Runs_food_municipalities_months.xlsx
@@ -456,7 +456,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -471,16 +471,16 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
       </c>
       <c r="K2">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -508,7 +508,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -523,21 +523,21 @@
         <v>14</v>
       </c>
       <c r="H4">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="I4">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
       </c>
       <c r="K4">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -552,10 +552,10 @@
         <v>14</v>
       </c>
       <c r="H5">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="I5">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
@@ -566,7 +566,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -581,21 +581,21 @@
         <v>14</v>
       </c>
       <c r="H6">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="I6">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
       </c>
       <c r="K6">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -633,21 +633,21 @@
         <v>14</v>
       </c>
       <c r="H8">
+        <v>0.54</v>
+      </c>
+      <c r="I8">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8">
         <v>0.53</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>0.52</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -662,21 +662,21 @@
         <v>14</v>
       </c>
       <c r="H9">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="I9">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="J9" t="s">
         <v>15</v>
       </c>
       <c r="K9">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -714,21 +714,21 @@
         <v>14</v>
       </c>
       <c r="H11">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
       </c>
       <c r="K11">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -746,7 +746,7 @@
         <v>0.54</v>
       </c>
       <c r="I12">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
@@ -757,7 +757,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -795,21 +795,21 @@
         <v>14</v>
       </c>
       <c r="H14">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="I14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J14" t="s">
         <v>15</v>
       </c>
       <c r="K14">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -827,7 +827,7 @@
         <v>0.47</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J15" t="s">
         <v>15</v>
@@ -838,7 +838,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
@@ -899,10 +899,10 @@
         <v>14</v>
       </c>
       <c r="H18">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I18">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
@@ -913,7 +913,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
@@ -931,18 +931,18 @@
         <v>0.53</v>
       </c>
       <c r="I19">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J19" t="s">
         <v>15</v>
       </c>
       <c r="K19">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
@@ -965,7 +965,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
@@ -980,10 +980,10 @@
         <v>14</v>
       </c>
       <c r="H21">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I21">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J21" t="s">
         <v>15</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
@@ -1009,21 +1009,21 @@
         <v>14</v>
       </c>
       <c r="H22">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="I22">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
       </c>
       <c r="K22">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
@@ -1061,21 +1061,21 @@
         <v>14</v>
       </c>
       <c r="H24">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="I24">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="J24" t="s">
         <v>15</v>
       </c>
       <c r="K24">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J25" t="s">
         <v>15</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
@@ -1142,21 +1142,21 @@
         <v>14</v>
       </c>
       <c r="H27">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J27" t="s">
         <v>15</v>
       </c>
       <c r="K27">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -1174,18 +1174,18 @@
         <v>0.58</v>
       </c>
       <c r="I28">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
       </c>
       <c r="K28">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="1">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
@@ -1203,18 +1203,18 @@
         <v>0.55</v>
       </c>
       <c r="I29">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
       </c>
       <c r="K29">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
@@ -1229,10 +1229,10 @@
         <v>14</v>
       </c>
       <c r="H30">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="I30">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
@@ -1258,21 +1258,21 @@
         <v>14</v>
       </c>
       <c r="H31">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="I31">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
       </c>
       <c r="K31">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
@@ -1290,7 +1290,7 @@
         <v>0.51</v>
       </c>
       <c r="I32">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="J32" t="s">
         <v>15</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="1">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
@@ -1339,10 +1339,10 @@
         <v>14</v>
       </c>
       <c r="H34">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I34">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J34" t="s">
         <v>15</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="1">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -1368,21 +1368,21 @@
         <v>14</v>
       </c>
       <c r="H35">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="I35">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="J35" t="s">
         <v>15</v>
       </c>
       <c r="K35">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="1">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
@@ -1405,7 +1405,7 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
@@ -1420,16 +1420,16 @@
         <v>14</v>
       </c>
       <c r="H37">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="I37">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="J37" t="s">
         <v>15</v>
       </c>
       <c r="K37">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>

--- a/Impact modelling/Runs_food_municipalities_months.xlsx
+++ b/Impact modelling/Runs_food_municipalities_months.xlsx
@@ -471,16 +471,16 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <v>0.46</v>
+        <v>0.18</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
       </c>
       <c r="K2">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -499,11 +499,17 @@
       <c r="G3" t="s">
         <v>14</v>
       </c>
+      <c r="H3">
+        <v>0.02</v>
+      </c>
       <c r="I3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
+      </c>
+      <c r="K3">
+        <v>0.04</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -522,17 +528,11 @@
       <c r="G4" t="s">
         <v>14</v>
       </c>
-      <c r="H4">
-        <v>0.49</v>
-      </c>
       <c r="I4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
-      </c>
-      <c r="K4">
-        <v>0.49</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -552,16 +552,16 @@
         <v>14</v>
       </c>
       <c r="H5">
-        <v>0.52</v>
+        <v>0.14</v>
       </c>
       <c r="I5">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
       </c>
       <c r="K5">
-        <v>0.49</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -581,16 +581,16 @@
         <v>14</v>
       </c>
       <c r="H6">
-        <v>0.49</v>
+        <v>0.05</v>
       </c>
       <c r="I6">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
       </c>
       <c r="K6">
-        <v>0.47</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -633,16 +633,16 @@
         <v>14</v>
       </c>
       <c r="H8">
-        <v>0.54</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I8">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J8" t="s">
         <v>15</v>
       </c>
       <c r="K8">
-        <v>0.53</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -662,16 +662,16 @@
         <v>14</v>
       </c>
       <c r="H9">
-        <v>0.59</v>
+        <v>0.11</v>
       </c>
       <c r="I9">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s">
         <v>15</v>
       </c>
       <c r="K9">
-        <v>0.59</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -714,16 +714,16 @@
         <v>14</v>
       </c>
       <c r="H11">
-        <v>0.6</v>
+        <v>-0.01</v>
       </c>
       <c r="I11">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
       </c>
       <c r="K11">
-        <v>0.57</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -743,16 +743,16 @@
         <v>14</v>
       </c>
       <c r="H12">
-        <v>0.54</v>
+        <v>0.2</v>
       </c>
       <c r="I12">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
       </c>
       <c r="K12">
-        <v>0.52</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -795,16 +795,16 @@
         <v>14</v>
       </c>
       <c r="H14">
-        <v>0.47</v>
+        <v>0.18</v>
       </c>
       <c r="I14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J14" t="s">
         <v>15</v>
       </c>
       <c r="K14">
-        <v>0.46</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -824,16 +824,16 @@
         <v>14</v>
       </c>
       <c r="H15">
-        <v>0.47</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J15" t="s">
         <v>15</v>
       </c>
       <c r="K15">
-        <v>0.47</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -875,11 +875,17 @@
       <c r="G17" t="s">
         <v>14</v>
       </c>
+      <c r="H17">
+        <v>0.12</v>
+      </c>
       <c r="I17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J17" t="s">
         <v>15</v>
+      </c>
+      <c r="K17">
+        <v>0.13</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -899,16 +905,16 @@
         <v>14</v>
       </c>
       <c r="H18">
-        <v>0.65</v>
+        <v>0.13</v>
       </c>
       <c r="I18">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
       </c>
       <c r="K18">
-        <v>0.68</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -928,16 +934,16 @@
         <v>14</v>
       </c>
       <c r="H19">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="I19">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="J19" t="s">
         <v>15</v>
       </c>
       <c r="K19">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -956,11 +962,17 @@
       <c r="G20" t="s">
         <v>14</v>
       </c>
+      <c r="H20">
+        <v>0.25</v>
+      </c>
       <c r="I20">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J20" t="s">
         <v>15</v>
+      </c>
+      <c r="K20">
+        <v>0.26</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -980,16 +992,16 @@
         <v>14</v>
       </c>
       <c r="H21">
-        <v>0.46</v>
+        <v>0.2</v>
       </c>
       <c r="I21">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="J21" t="s">
         <v>15</v>
       </c>
       <c r="K21">
-        <v>0.44</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1009,16 +1021,16 @@
         <v>14</v>
       </c>
       <c r="H22">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="I22">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
       </c>
       <c r="K22">
-        <v>0.76</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1037,11 +1049,17 @@
       <c r="G23" t="s">
         <v>14</v>
       </c>
+      <c r="H23">
+        <v>0.16</v>
+      </c>
       <c r="I23">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
+      </c>
+      <c r="K23">
+        <v>0.16</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1061,16 +1079,16 @@
         <v>14</v>
       </c>
       <c r="H24">
-        <v>0.61</v>
+        <v>0.08</v>
       </c>
       <c r="I24">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J24" t="s">
         <v>15</v>
       </c>
       <c r="K24">
-        <v>0.63</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1090,16 +1108,16 @@
         <v>14</v>
       </c>
       <c r="H25">
-        <v>0.5600000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="J25" t="s">
         <v>15</v>
       </c>
       <c r="K25">
-        <v>0.5600000000000001</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1118,11 +1136,17 @@
       <c r="G26" t="s">
         <v>14</v>
       </c>
+      <c r="H26">
+        <v>0.37</v>
+      </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="s">
         <v>15</v>
+      </c>
+      <c r="K26">
+        <v>0.37</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1142,16 +1166,16 @@
         <v>14</v>
       </c>
       <c r="H27">
-        <v>0.85</v>
+        <v>0.14</v>
       </c>
       <c r="I27">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J27" t="s">
         <v>15</v>
       </c>
       <c r="K27">
-        <v>0.83</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1171,16 +1195,16 @@
         <v>14</v>
       </c>
       <c r="H28">
-        <v>0.58</v>
+        <v>0.32</v>
       </c>
       <c r="I28">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
       </c>
       <c r="K28">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1200,16 +1224,16 @@
         <v>14</v>
       </c>
       <c r="H29">
-        <v>0.55</v>
+        <v>0.26</v>
       </c>
       <c r="I29">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
       </c>
       <c r="K29">
-        <v>0.53</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1229,16 +1253,16 @@
         <v>14</v>
       </c>
       <c r="H30">
-        <v>0.5</v>
+        <v>-0.11</v>
       </c>
       <c r="I30">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
       </c>
       <c r="K30">
-        <v>0.47</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1258,16 +1282,16 @@
         <v>14</v>
       </c>
       <c r="H31">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
       <c r="I31">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
       </c>
       <c r="K31">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1287,16 +1311,16 @@
         <v>14</v>
       </c>
       <c r="H32">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="I32">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="J32" t="s">
         <v>15</v>
       </c>
       <c r="K32">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1315,11 +1339,17 @@
       <c r="G33" t="s">
         <v>14</v>
       </c>
+      <c r="H33">
+        <v>0.41</v>
+      </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="s">
         <v>15</v>
+      </c>
+      <c r="K33">
+        <v>0.41</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1339,16 +1369,16 @@
         <v>14</v>
       </c>
       <c r="H34">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
       <c r="I34">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="J34" t="s">
         <v>15</v>
       </c>
       <c r="K34">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1368,16 +1398,16 @@
         <v>14</v>
       </c>
       <c r="H35">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="I35">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="J35" t="s">
         <v>15</v>
       </c>
       <c r="K35">
-        <v>0.5</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1396,11 +1426,17 @@
       <c r="G36" t="s">
         <v>14</v>
       </c>
+      <c r="H36">
+        <v>0.03</v>
+      </c>
       <c r="I36">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J36" t="s">
         <v>15</v>
+      </c>
+      <c r="K36">
+        <v>0.03</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1420,16 +1456,16 @@
         <v>14</v>
       </c>
       <c r="H37">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="I37">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="J37" t="s">
         <v>15</v>
       </c>
       <c r="K37">
-        <v>0.54</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
